--- a/태화라이온스 회원명부.xlsx
+++ b/태화라이온스 회원명부.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\이재원\클로드코딩\태화라이온스\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23002D1A-42BA-4AFE-B826-5863BA6C4FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3732E23-26FE-4A24-90CB-6099AE5F8C1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="111">
   <si>
     <t>장태원</t>
   </si>
@@ -304,9 +304,6 @@
   </si>
   <si>
     <t>제21대 회장</t>
-  </si>
-  <si>
-    <t>일련번호</t>
   </si>
   <si>
     <t>3부회장</t>
@@ -366,10 +363,6 @@
     <t>제35대 회장
 기획위원장
 골프총무</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>태화라이온스클럽 회원명부</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -414,7 +407,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -451,21 +444,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="double">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -476,49 +454,6 @@
         <color auto="1"/>
       </top>
       <bottom style="double">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -544,7 +479,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -561,18 +496,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1050,623 +973,489 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.375" customWidth="1"/>
-    <col min="3" max="3" width="58.75" customWidth="1"/>
-    <col min="4" max="4" width="20.625" customWidth="1"/>
+    <col min="1" max="1" width="11.375" customWidth="1"/>
+    <col min="2" max="2" width="58.75" customWidth="1"/>
+    <col min="3" max="3" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-    </row>
-    <row r="2" spans="1:4" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="7"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+    </row>
+    <row r="2" spans="1:3" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="48.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="48.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="6">
+      <c r="C7" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="6">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="B35" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="7">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7">
-        <v>4</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="7">
-        <v>5</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7">
-        <v>6</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="7">
+      <c r="B36" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7">
-        <v>8</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="7">
-        <v>9</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7">
-        <v>10</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="7">
-        <v>11</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="7">
-        <v>12</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="7">
+      <c r="B41" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="7">
-        <v>14</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="7">
-        <v>15</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="7">
-        <v>16</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="7">
-        <v>17</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="7">
-        <v>18</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="7">
-        <v>19</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="7">
-        <v>20</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="7">
-        <v>21</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="7">
-        <v>22</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="7">
-        <v>23</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="7">
-        <v>24</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="7">
-        <v>25</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="7">
-        <v>26</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="7">
-        <v>27</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="7">
-        <v>28</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="7">
-        <v>29</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="7">
-        <v>30</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="7">
-        <v>31</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="7">
+      <c r="B42" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="7">
-        <v>33</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="7">
-        <v>34</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="7">
-        <v>35</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="7">
-        <v>36</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="7">
-        <v>37</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="7">
-        <v>38</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="7">
-        <v>39</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="7">
-        <v>40</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="8">
-        <v>41</v>
-      </c>
-      <c r="B43" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D43" s="9" t="s">
+      <c r="B43" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C43" s="5" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="10"/>
-      <c r="B44" s="10"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="10"/>
-    </row>
-    <row r="45" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A45" s="10"/>
+    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="6"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.15388889610767365" bottom="6.9583334028720856E-2" header="0.21638889610767365" footer="0.14569444954395294"/>

--- a/태화라이온스 회원명부.xlsx
+++ b/태화라이온스 회원명부.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\이재원\클로드코딩\태화라이온스\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3732E23-26FE-4A24-90CB-6099AE5F8C1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38D35030-DA2C-4991-803C-CDC5D492158B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -341,13 +341,7 @@
 봉사특별위원회위원</t>
   </si>
   <si>
-    <t>회원(산악총무)</t>
-  </si>
-  <si>
     <t>제36대회장</t>
-  </si>
-  <si>
-    <t>태화라이온스 38대 현회장</t>
   </si>
   <si>
     <t>1부회장
@@ -360,9 +354,18 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>제 38대 현회장</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>회원
+산악회 총무</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>제35대 회장
 기획위원장
-골프총무</t>
+골프회 총무</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1002,7 +1005,7 @@
         <v>38</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>72</v>
@@ -1024,7 +1027,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>75</v>
@@ -1035,7 +1038,7 @@
         <v>30</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>82</v>
@@ -1244,7 +1247,7 @@
         <v>46</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>64</v>
@@ -1408,8 +1411,8 @@
       <c r="A40" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>105</v>
+      <c r="B40" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>101</v>

--- a/태화라이온스 회원명부.xlsx
+++ b/태화라이온스 회원명부.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\이재원\클로드코딩\태화라이온스\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38D35030-DA2C-4991-803C-CDC5D492158B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C9F9131-4376-4982-ADE2-7D6B1A998B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -160,9 +160,6 @@
     <t>이재원</t>
   </si>
   <si>
-    <t>주승대</t>
-  </si>
-  <si>
     <t>010-3862-0489</t>
   </si>
   <si>
@@ -328,9 +325,6 @@
   </si>
   <si>
     <t>010-4859-3083</t>
-  </si>
-  <si>
-    <t>010-9408-5570</t>
   </si>
   <si>
     <t>초대 및 2대 회장
@@ -366,6 +360,14 @@
     <t>제35대 회장
 기획위원장
 골프회 총무</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>주성대</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>010-3408-5570</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1005,10 +1007,10 @@
         <v>38</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1016,10 +1018,10 @@
         <v>24</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1027,10 +1029,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1038,10 +1040,10 @@
         <v>30</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1049,10 +1051,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1060,10 +1062,10 @@
         <v>0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1071,10 +1073,10 @@
         <v>45</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1085,7 +1087,7 @@
         <v>18</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1096,7 +1098,7 @@
         <v>19</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1104,10 +1106,10 @@
         <v>27</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1115,10 +1117,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1126,10 +1128,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1137,10 +1139,10 @@
         <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1148,10 +1150,10 @@
         <v>22</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1159,10 +1161,10 @@
         <v>43</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1170,10 +1172,10 @@
         <v>26</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1181,10 +1183,10 @@
         <v>41</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1192,10 +1194,10 @@
         <v>35</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1203,10 +1205,10 @@
         <v>44</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1214,10 +1216,10 @@
         <v>23</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1225,10 +1227,10 @@
         <v>28</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1236,21 +1238,21 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>46</v>
+        <v>109</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1261,7 +1263,7 @@
         <v>20</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1272,7 +1274,7 @@
         <v>20</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1283,7 +1285,7 @@
         <v>20</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1294,7 +1296,7 @@
         <v>20</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1305,7 +1307,7 @@
         <v>20</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1316,7 +1318,7 @@
         <v>20</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1327,7 +1329,7 @@
         <v>20</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1338,7 +1340,7 @@
         <v>20</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1349,7 +1351,7 @@
         <v>20</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1360,18 +1362,18 @@
         <v>20</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1382,7 +1384,7 @@
         <v>20</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1393,7 +1395,7 @@
         <v>15</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1404,7 +1406,7 @@
         <v>20</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1412,10 +1414,10 @@
         <v>17</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1426,7 +1428,7 @@
         <v>20</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1437,7 +1439,7 @@
         <v>20</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -1448,7 +1450,7 @@
         <v>20</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">

--- a/태화라이온스 회원명부.xlsx
+++ b/태화라이온스 회원명부.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\이재원\클로드코딩\태화라이온스\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C9F9131-4376-4982-ADE2-7D6B1A998B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90198ADB-2583-49F3-B5A0-858AC5907BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -348,10 +348,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>제 38대 현회장</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>회원
 산악회 총무</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -368,6 +364,10 @@
   </si>
   <si>
     <t>010-3408-5570</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>제38대 현회장</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1007,7 +1007,7 @@
         <v>38</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>71</v>
@@ -1238,7 +1238,7 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>57</v>
@@ -1246,7 +1246,7 @@
     </row>
     <row r="25" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>103</v>
@@ -1373,7 +1373,7 @@
         <v>20</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1414,7 +1414,7 @@
         <v>17</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>100</v>

--- a/태화라이온스 회원명부.xlsx
+++ b/태화라이온스 회원명부.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\이재원\클로드코딩\태화라이온스\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90198ADB-2583-49F3-B5A0-858AC5907BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5F42F3C-4BD0-4C41-9FA0-45882233FDC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-51720" yWindow="-5475" windowWidth="51840" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="113">
   <si>
     <t>장태원</t>
   </si>
@@ -368,6 +368,14 @@
   </si>
   <si>
     <t>제38대 현회장</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>회비납부</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>O</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -412,7 +420,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -435,56 +443,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="double">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -494,20 +459,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -978,7 +940,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.375" customWidth="1"/>
@@ -986,45 +948,50 @@
     <col min="3" max="3" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="7"/>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-    </row>
-    <row r="2" spans="1:3" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
+    <row r="1" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+    </row>
+    <row r="2" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="48.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="D2" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="D3" s="6"/>
+    </row>
+    <row r="4" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="1" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D4" s="6"/>
+    </row>
+    <row r="5" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -1034,8 +1001,9 @@
       <c r="C5" s="1" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D5" s="6"/>
+    </row>
+    <row r="6" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>30</v>
       </c>
@@ -1045,8 +1013,9 @@
       <c r="C6" s="1" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D6" s="6"/>
+    </row>
+    <row r="7" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>2</v>
       </c>
@@ -1056,8 +1025,9 @@
       <c r="C7" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D7" s="6"/>
+    </row>
+    <row r="8" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
@@ -1067,8 +1037,9 @@
       <c r="C8" s="1" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D8" s="6"/>
+    </row>
+    <row r="9" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>45</v>
       </c>
@@ -1078,8 +1049,11 @@
       <c r="C9" s="1" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D9" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
@@ -1089,8 +1063,9 @@
       <c r="C10" s="1" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D10" s="6"/>
+    </row>
+    <row r="11" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>3</v>
       </c>
@@ -1100,8 +1075,9 @@
       <c r="C11" s="1" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D11" s="6"/>
+    </row>
+    <row r="12" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>27</v>
       </c>
@@ -1111,8 +1087,9 @@
       <c r="C12" s="1" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D12" s="6"/>
+    </row>
+    <row r="13" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1122,8 +1099,9 @@
       <c r="C13" s="1" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D13" s="6"/>
+    </row>
+    <row r="14" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>14</v>
       </c>
@@ -1133,8 +1111,9 @@
       <c r="C14" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D14" s="6"/>
+    </row>
+    <row r="15" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>21</v>
       </c>
@@ -1144,8 +1123,9 @@
       <c r="C15" s="1" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D15" s="6"/>
+    </row>
+    <row r="16" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>22</v>
       </c>
@@ -1155,8 +1135,9 @@
       <c r="C16" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D16" s="6"/>
+    </row>
+    <row r="17" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>43</v>
       </c>
@@ -1166,8 +1147,9 @@
       <c r="C17" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D17" s="6"/>
+    </row>
+    <row r="18" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
@@ -1177,8 +1159,9 @@
       <c r="C18" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D18" s="6"/>
+    </row>
+    <row r="19" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>41</v>
       </c>
@@ -1188,8 +1171,9 @@
       <c r="C19" s="1" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D19" s="6"/>
+    </row>
+    <row r="20" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>35</v>
       </c>
@@ -1199,8 +1183,9 @@
       <c r="C20" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D20" s="6"/>
+    </row>
+    <row r="21" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>44</v>
       </c>
@@ -1210,8 +1195,11 @@
       <c r="C21" s="1" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D21" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>23</v>
       </c>
@@ -1221,8 +1209,9 @@
       <c r="C22" s="1" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D22" s="6"/>
+    </row>
+    <row r="23" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>28</v>
       </c>
@@ -1232,8 +1221,9 @@
       <c r="C23" s="1" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D23" s="6"/>
+    </row>
+    <row r="24" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>25</v>
       </c>
@@ -1243,8 +1233,9 @@
       <c r="C24" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D24" s="6"/>
+    </row>
+    <row r="25" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>108</v>
       </c>
@@ -1254,8 +1245,9 @@
       <c r="C25" s="1" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D25" s="6"/>
+    </row>
+    <row r="26" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>33</v>
       </c>
@@ -1265,8 +1257,9 @@
       <c r="C26" s="1" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D26" s="6"/>
+    </row>
+    <row r="27" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>31</v>
       </c>
@@ -1276,8 +1269,9 @@
       <c r="C27" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D27" s="6"/>
+    </row>
+    <row r="28" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>34</v>
       </c>
@@ -1287,8 +1281,9 @@
       <c r="C28" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D28" s="6"/>
+    </row>
+    <row r="29" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>4</v>
       </c>
@@ -1298,8 +1293,9 @@
       <c r="C29" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D29" s="6"/>
+    </row>
+    <row r="30" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>37</v>
       </c>
@@ -1309,8 +1305,9 @@
       <c r="C30" s="1" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D30" s="6"/>
+    </row>
+    <row r="31" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>39</v>
       </c>
@@ -1320,8 +1317,9 @@
       <c r="C31" s="1" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D31" s="6"/>
+    </row>
+    <row r="32" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>42</v>
       </c>
@@ -1331,8 +1329,9 @@
       <c r="C32" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D32" s="6"/>
+    </row>
+    <row r="33" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>36</v>
       </c>
@@ -1342,8 +1341,9 @@
       <c r="C33" s="1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D33" s="6"/>
+    </row>
+    <row r="34" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>40</v>
       </c>
@@ -1353,8 +1353,9 @@
       <c r="C34" s="1" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D34" s="6"/>
+    </row>
+    <row r="35" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>1</v>
       </c>
@@ -1364,8 +1365,9 @@
       <c r="C35" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D35" s="6"/>
+    </row>
+    <row r="36" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>99</v>
       </c>
@@ -1375,8 +1377,9 @@
       <c r="C36" s="1" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D36" s="6"/>
+    </row>
+    <row r="37" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>29</v>
       </c>
@@ -1386,8 +1389,9 @@
       <c r="C37" s="1" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D37" s="6"/>
+    </row>
+    <row r="38" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>11</v>
       </c>
@@ -1397,8 +1401,11 @@
       <c r="C38" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D38" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>10</v>
       </c>
@@ -1408,8 +1415,11 @@
       <c r="C39" s="1" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D39" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>17</v>
       </c>
@@ -1419,8 +1429,9 @@
       <c r="C40" s="1" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D40" s="6"/>
+    </row>
+    <row r="41" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>7</v>
       </c>
@@ -1430,8 +1441,9 @@
       <c r="C41" s="1" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D41" s="6"/>
+    </row>
+    <row r="42" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>13</v>
       </c>
@@ -1441,22 +1453,24 @@
       <c r="C42" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="5" t="s">
+      <c r="D42" s="6"/>
+    </row>
+    <row r="43" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C43" s="5" t="s">
+      <c r="B43" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="6"/>
-      <c r="B44" s="6"/>
-      <c r="C44" s="6"/>
+      <c r="D43" s="6"/>
+    </row>
+    <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="3"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/태화라이온스 회원명부.xlsx
+++ b/태화라이온스 회원명부.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\이재원\클로드코딩\태화라이온스\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5F42F3C-4BD0-4C41-9FA0-45882233FDC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEC7DE48-BE67-4E54-AE79-5C41B1A3AD5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-51720" yWindow="-5475" windowWidth="51840" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="115">
   <si>
     <t>장태원</t>
   </si>
@@ -376,6 +376,14 @@
   </si>
   <si>
     <t>O</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>정윤제</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>010-6769-8114</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -449,7 +457,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -459,17 +467,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -963,7 +965,7 @@
       <c r="C2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="1" t="s">
         <v>111</v>
       </c>
     </row>
@@ -977,7 +979,7 @@
       <c r="C3" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D3" s="6"/>
+      <c r="D3" s="3"/>
     </row>
     <row r="4" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -989,7 +991,7 @@
       <c r="C4" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D4" s="6"/>
+      <c r="D4" s="3"/>
     </row>
     <row r="5" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -1001,7 +1003,9 @@
       <c r="C5" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D5" s="6"/>
+      <c r="D5" s="1" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="6" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
@@ -1013,7 +1017,7 @@
       <c r="C6" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D6" s="6"/>
+      <c r="D6" s="3"/>
     </row>
     <row r="7" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
@@ -1025,7 +1029,7 @@
       <c r="C7" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="6"/>
+      <c r="D7" s="3"/>
     </row>
     <row r="8" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -1037,7 +1041,7 @@
       <c r="C8" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D8" s="6"/>
+      <c r="D8" s="3"/>
     </row>
     <row r="9" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
@@ -1049,7 +1053,7 @@
       <c r="C9" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="1" t="s">
         <v>112</v>
       </c>
     </row>
@@ -1063,7 +1067,7 @@
       <c r="C10" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D10" s="6"/>
+      <c r="D10" s="3"/>
     </row>
     <row r="11" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
@@ -1075,7 +1079,7 @@
       <c r="C11" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="6"/>
+      <c r="D11" s="3"/>
     </row>
     <row r="12" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
@@ -1087,7 +1091,7 @@
       <c r="C12" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D12" s="6"/>
+      <c r="D12" s="3"/>
     </row>
     <row r="13" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
@@ -1099,7 +1103,7 @@
       <c r="C13" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D13" s="6"/>
+      <c r="D13" s="3"/>
     </row>
     <row r="14" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
@@ -1111,7 +1115,7 @@
       <c r="C14" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="6"/>
+      <c r="D14" s="3"/>
     </row>
     <row r="15" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
@@ -1123,7 +1127,7 @@
       <c r="C15" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D15" s="6"/>
+      <c r="D15" s="3"/>
     </row>
     <row r="16" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
@@ -1135,7 +1139,7 @@
       <c r="C16" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="6"/>
+      <c r="D16" s="3"/>
     </row>
     <row r="17" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
@@ -1147,7 +1151,7 @@
       <c r="C17" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="6"/>
+      <c r="D17" s="3"/>
     </row>
     <row r="18" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
@@ -1159,7 +1163,7 @@
       <c r="C18" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="6"/>
+      <c r="D18" s="3"/>
     </row>
     <row r="19" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
@@ -1171,7 +1175,7 @@
       <c r="C19" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D19" s="6"/>
+      <c r="D19" s="3"/>
     </row>
     <row r="20" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
@@ -1183,7 +1187,7 @@
       <c r="C20" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="6"/>
+      <c r="D20" s="3"/>
     </row>
     <row r="21" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
@@ -1195,7 +1199,7 @@
       <c r="C21" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="1" t="s">
         <v>112</v>
       </c>
     </row>
@@ -1209,7 +1213,7 @@
       <c r="C22" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D22" s="6"/>
+      <c r="D22" s="3"/>
     </row>
     <row r="23" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
@@ -1221,7 +1225,7 @@
       <c r="C23" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D23" s="6"/>
+      <c r="D23" s="3"/>
     </row>
     <row r="24" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
@@ -1233,7 +1237,7 @@
       <c r="C24" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D24" s="6"/>
+      <c r="D24" s="3"/>
     </row>
     <row r="25" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
@@ -1245,7 +1249,7 @@
       <c r="C25" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D25" s="6"/>
+      <c r="D25" s="3"/>
     </row>
     <row r="26" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
@@ -1257,7 +1261,7 @@
       <c r="C26" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D26" s="6"/>
+      <c r="D26" s="3"/>
     </row>
     <row r="27" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
@@ -1269,7 +1273,7 @@
       <c r="C27" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D27" s="6"/>
+      <c r="D27" s="3"/>
     </row>
     <row r="28" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
@@ -1281,7 +1285,7 @@
       <c r="C28" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D28" s="6"/>
+      <c r="D28" s="3"/>
     </row>
     <row r="29" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
@@ -1293,7 +1297,7 @@
       <c r="C29" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D29" s="6"/>
+      <c r="D29" s="3"/>
     </row>
     <row r="30" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
@@ -1305,7 +1309,7 @@
       <c r="C30" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D30" s="6"/>
+      <c r="D30" s="3"/>
     </row>
     <row r="31" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
@@ -1317,7 +1321,7 @@
       <c r="C31" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D31" s="6"/>
+      <c r="D31" s="3"/>
     </row>
     <row r="32" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
@@ -1329,7 +1333,7 @@
       <c r="C32" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D32" s="6"/>
+      <c r="D32" s="3"/>
     </row>
     <row r="33" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
@@ -1341,7 +1345,7 @@
       <c r="C33" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D33" s="6"/>
+      <c r="D33" s="3"/>
     </row>
     <row r="34" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
@@ -1353,7 +1357,7 @@
       <c r="C34" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D34" s="6"/>
+      <c r="D34" s="3"/>
     </row>
     <row r="35" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
@@ -1365,7 +1369,7 @@
       <c r="C35" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D35" s="6"/>
+      <c r="D35" s="3"/>
     </row>
     <row r="36" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
@@ -1377,7 +1381,7 @@
       <c r="C36" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D36" s="6"/>
+      <c r="D36" s="3"/>
     </row>
     <row r="37" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
@@ -1389,7 +1393,7 @@
       <c r="C37" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D37" s="6"/>
+      <c r="D37" s="3"/>
     </row>
     <row r="38" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
@@ -1401,7 +1405,7 @@
       <c r="C38" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="D38" s="1" t="s">
         <v>112</v>
       </c>
     </row>
@@ -1415,7 +1419,7 @@
       <c r="C39" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="D39" s="1" t="s">
         <v>112</v>
       </c>
     </row>
@@ -1429,7 +1433,9 @@
       <c r="C40" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D40" s="6"/>
+      <c r="D40" s="1" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="41" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
@@ -1441,7 +1447,7 @@
       <c r="C41" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D41" s="6"/>
+      <c r="D41" s="3"/>
     </row>
     <row r="42" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
@@ -1453,7 +1459,7 @@
       <c r="C42" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D42" s="6"/>
+      <c r="D42" s="3"/>
     </row>
     <row r="43" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
@@ -1465,12 +1471,21 @@
       <c r="C43" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D43" s="6"/>
+      <c r="D43" s="3"/>
     </row>
     <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="3"/>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
+      <c r="A44" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>112</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
